--- a/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlPositionAnalysis002.xlsx
+++ b/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlPositionAnalysis002.xlsx
@@ -1,334 +1,598 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16635" windowHeight="3540"/>
+    <workbookView windowWidth="19815" windowHeight="8970"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>组合代码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产代码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>持仓市值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>应计利息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>公允价格</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>持仓数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>名义本金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>持仓成本</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>发行主体</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>是否国企</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>是否上市公司</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>企业性质</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>所属行业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>行业二级分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产起息日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产到期日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>期限（天）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>交易对手</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>剩余期限（年）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>最近交易日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>金融产品代码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>分支序号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>是否穿透</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产一级分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产二级分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产三级分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产四级分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产五级分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>持仓券面总额</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>发行券面总额</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>票面利率%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>成本收益率%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>估价收益率%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>久期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>修正久期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>凸性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>含权信息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>下一行权日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>剩余行权期限（年）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>主体评级</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>主体评级机构</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>债项评级</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>债项评级机构</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>主体评级（内部）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>债项评级（内部）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>主体评级机构（内部）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>债项评级机构（内部）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>是否城投债</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>所属地区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">流通股本 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>总股本</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>交易场所</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>是否永续</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>是否含权债</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>含权摊销日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>持仓规模</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>收益类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>价格涨跌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>价格涨跌幅%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>持仓占发行总额比%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>持仓占债券资产规模比%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>持仓占总股本比%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>持仓占流通股本比%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机构名称</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -336,39 +600,325 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -417,7 +967,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -452,7 +1002,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -655,14 +1205,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BN1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:BO1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
@@ -715,10 +1265,11 @@
     <col min="64" max="64" width="23.25" style="1" customWidth="1"/>
     <col min="65" max="65" width="17.25" style="1" customWidth="1"/>
     <col min="66" max="66" width="18.5" style="1" customWidth="1"/>
-    <col min="67" max="16384" width="9" style="1"/>
+    <col min="67" max="67" width="16.75" style="1" customWidth="1"/>
+    <col min="68" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:67">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -917,30 +1468,35 @@
       <c r="BN1" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="BO1" s="5" t="s">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlPositionAnalysis002.xlsx
+++ b/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlPositionAnalysis002.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpaceZhu\tams-invest-parent\tams-invest-portfolio\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="8970"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="8970"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>分类</t>
   </si>
@@ -216,22 +221,28 @@
     <t>持仓占流通股本比%</t>
   </si>
   <si>
+    <t>基点价值</t>
+  </si>
+  <si>
+    <t>浮盈浮亏</t>
+  </si>
+  <si>
+    <t>浮盈浮亏（单价）</t>
+  </si>
+  <si>
     <t>机构名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,356 +254,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -600,251 +282,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -864,61 +304,17 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -967,7 +363,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1002,7 +398,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1205,71 +601,73 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:BO1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BR1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" style="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.25" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="15.875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="14.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.7265625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.90625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="15.90625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" style="3" customWidth="1"/>
     <col min="14" max="15" width="9" style="1"/>
-    <col min="16" max="16" width="13.75" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.5" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.75" style="1" customWidth="1"/>
-    <col min="20" max="20" width="13.125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7265625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.36328125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.453125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.7265625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="13.08984375" style="1" customWidth="1"/>
     <col min="21" max="21" width="16" style="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5" style="1" customWidth="1"/>
-    <col min="23" max="23" width="14.875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="13.453125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="14.90625" style="1" customWidth="1"/>
     <col min="24" max="26" width="9" style="1"/>
-    <col min="27" max="27" width="14.125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="12.625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.375" style="1" customWidth="1"/>
-    <col min="30" max="30" width="14.25" style="1" customWidth="1"/>
+    <col min="27" max="27" width="14.08984375" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12.6328125" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.36328125" style="1" customWidth="1"/>
+    <col min="30" max="30" width="14.26953125" style="1" customWidth="1"/>
     <col min="31" max="31" width="14" style="1" customWidth="1"/>
-    <col min="32" max="33" width="13.625" style="1" customWidth="1"/>
+    <col min="32" max="33" width="13.6328125" style="1" customWidth="1"/>
     <col min="34" max="34" width="9" style="1"/>
-    <col min="35" max="35" width="15.625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="13.25" style="1" customWidth="1"/>
+    <col min="35" max="35" width="15.6328125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="13.26953125" style="1" customWidth="1"/>
     <col min="37" max="40" width="9" style="1"/>
-    <col min="41" max="41" width="10.5" style="1" customWidth="1"/>
-    <col min="42" max="42" width="18.5" style="1" customWidth="1"/>
-    <col min="43" max="43" width="11.5" style="1" customWidth="1"/>
-    <col min="44" max="44" width="11.75" style="1" customWidth="1"/>
-    <col min="45" max="45" width="11.25" style="1" customWidth="1"/>
+    <col min="41" max="41" width="10.453125" style="1" customWidth="1"/>
+    <col min="42" max="42" width="18.453125" style="1" customWidth="1"/>
+    <col min="43" max="43" width="11.453125" style="1" customWidth="1"/>
+    <col min="44" max="44" width="11.7265625" style="1" customWidth="1"/>
+    <col min="45" max="45" width="11.26953125" style="1" customWidth="1"/>
     <col min="46" max="46" width="12" style="1" customWidth="1"/>
-    <col min="47" max="47" width="12.125" style="1" customWidth="1"/>
+    <col min="47" max="47" width="12.08984375" style="1" customWidth="1"/>
     <col min="48" max="48" width="18" style="1" customWidth="1"/>
-    <col min="49" max="49" width="15.75" style="1" customWidth="1"/>
-    <col min="50" max="50" width="18.75" style="1" customWidth="1"/>
+    <col min="49" max="49" width="15.7265625" style="1" customWidth="1"/>
+    <col min="50" max="50" width="18.7265625" style="1" customWidth="1"/>
     <col min="51" max="57" width="9" style="1"/>
     <col min="58" max="58" width="12" style="1" customWidth="1"/>
     <col min="59" max="61" width="9" style="1"/>
-    <col min="62" max="62" width="13.125" style="1" customWidth="1"/>
+    <col min="62" max="62" width="13.08984375" style="1" customWidth="1"/>
     <col min="63" max="63" width="18" style="1" customWidth="1"/>
-    <col min="64" max="64" width="23.25" style="1" customWidth="1"/>
-    <col min="65" max="65" width="17.25" style="1" customWidth="1"/>
-    <col min="66" max="66" width="18.5" style="1" customWidth="1"/>
-    <col min="67" max="67" width="16.75" style="1" customWidth="1"/>
-    <col min="68" max="16384" width="9" style="1"/>
+    <col min="64" max="64" width="23.26953125" style="1" customWidth="1"/>
+    <col min="65" max="65" width="17.26953125" style="1" customWidth="1"/>
+    <col min="66" max="66" width="18.453125" style="1" customWidth="1"/>
+    <col min="67" max="67" width="16.7265625" style="1" customWidth="1"/>
+    <col min="68" max="68" width="9" style="1"/>
+    <col min="69" max="69" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1471,32 +869,39 @@
       <c r="BO1" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="BP1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="5" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>